--- a/Templates/Template_CKGSekolah.xlsx
+++ b/Templates/Template_CKGSekolah.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lihan\AUTOMATION\AutoCKG\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4B75E9-C952-477E-8F98-08FC53D867E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E647BFA-300B-43AF-908A-0249167256B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <author>Lihan</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{1CFFBA18-6626-478A-A59D-B35B1C00FCAA}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{6419F8AD-4631-4F72-9310-8B12CFE6497B}">
       <text>
         <r>
           <rPr>
@@ -40,7 +40,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{17D538AF-4C4E-4C7D-ACF8-FB1ABDFDFA33}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{141BFD3F-D93C-4DC7-BDF6-9BC33EA17D36}">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{2B7F08CA-29E4-4C9E-B968-0CD5C5A5A8C4}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{A3AF9E45-18A4-4DB0-AE86-2FAEFE77B5B0}">
       <text>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{4D4DD7E4-D7D7-4DA6-9EC3-E0CA1F38AA23}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{69122EEA-BEDD-408D-8F87-A3B6427D31DE}">
       <text>
         <r>
           <rPr>
@@ -82,52 +82,35 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{99A7A7F9-4652-4179-9E34-71A895792CEA}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>BELUM MENIKAH
-MENIKAH
-CERAI HIDUP
-CERAI MATI</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{DF7E7A33-5DC6-4A1F-89B1-93014DC42958}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>TIDAK MEMILIKI DISABILITAS atau NON DISABILITAS</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{6A84141E-7855-40B9-A7ED-F4BD0A68DAB2}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>IYA atau TIDAK</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{21972537-0A90-40E5-8B3E-8E92272FA98D}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{1A950CB6-AF29-4D62-8D15-807950A0E631}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>isi sesuai nama sekkolah harus sama dengan di apk ckg</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{A88E73F3-B90D-4D69-B32A-A560E292903F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>copas atau isi dengan angka kelasnya sajja</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{1AB2D2D4-6C0F-43BB-9B67-BD0A5CE3A769}">
       <text>
         <r>
           <rPr>
@@ -151,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{11623C59-42F7-4F81-A463-223B6E7A3060}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{5BDAFB53-59E1-4674-B378-34ED38AC062A}">
       <text>
         <r>
           <rPr>
@@ -165,21 +148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{14369DFC-FE53-43F4-9D7B-1BBB8E07FAC0}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>NORMAL atau ANGKA YANG NYATA</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{508C4B91-0AFD-44BD-9FBD-FACF8FA761B3}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{CE41EE18-E256-4E92-B2B8-A4EA0350AC31}">
       <text>
         <r>
           <rPr>
@@ -193,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{C13FCA42-FA3F-4A7A-BC9A-043D98805E7F}">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{2429B205-2237-40BB-BBE9-B2E888F6B61C}">
       <text>
         <r>
           <rPr>
@@ -207,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{FFAD6C85-AA1C-4778-8884-EF0E20A9EF58}">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{0FF60822-D7CF-4D34-BB7F-E278BA30823A}">
       <text>
         <r>
           <rPr>
@@ -221,59 +190,83 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{2D856BCC-1812-4A36-AA33-9023D1A6FA67}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>TIDAK atau IYA</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{5F030FC4-6D06-4A22-9494-F07D8D29F53A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>TIDAK</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{68E6974F-2AA1-4456-96A6-56D43475DD6E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>NORMAL</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{86E686B6-50BA-4164-9CBF-7EAAFF184E1F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>IYA atau TIDAK</t>
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{9DA5EC6A-EB27-4D94-95D2-F6177942CA95}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>bisa ditulis NORMAL atau ANGKA YANG NYATA</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{97D3A1A5-C211-408C-AD24-49564669D816}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>hanya bisa ditulis (TIDAK ADA,1,2 atau 3)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{034DA75A-95E0-4DD0-A2BB-A100C60D73FB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>range 1-7</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{DCC4A618-8A36-4D6A-9558-4F17E80D3F0D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>range 1-7</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{14691BE5-0345-4D9A-93BD-9CDFDE39AD6F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>kosongi aja, nanti otomatis ke isi</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
@@ -362,7 +355,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
   <si>
     <t>NIK</t>
   </si>
@@ -418,51 +411,9 @@
     <t>notif</t>
   </si>
   <si>
-    <t>Provinsi</t>
-  </si>
-  <si>
-    <t>Kota</t>
-  </si>
-  <si>
-    <t>Kecamatan</t>
-  </si>
-  <si>
-    <t>Kelurahan</t>
-  </si>
-  <si>
-    <t>Lainnya</t>
-  </si>
-  <si>
-    <t>Hamil</t>
-  </si>
-  <si>
-    <t>Status Pernikahan</t>
-  </si>
-  <si>
-    <t>Penyandang Disabilitas</t>
-  </si>
-  <si>
-    <t>Pekerjaan</t>
-  </si>
-  <si>
-    <t>Lingkar Perut</t>
-  </si>
-  <si>
-    <t>Faktor Risiko Kanker Usus</t>
-  </si>
-  <si>
     <t>TIDAK</t>
   </si>
   <si>
-    <t>Faktor Risiko TB - Dewasa &amp; Lansia</t>
-  </si>
-  <si>
-    <t>Hati</t>
-  </si>
-  <si>
-    <t>Kanker Leher Rahim</t>
-  </si>
-  <si>
     <t>Kesehatan Jiwa</t>
   </si>
   <si>
@@ -481,49 +432,112 @@
     <t>Tingkat Aktivitas Fisik (sedang dan berat)</t>
   </si>
   <si>
-    <t>Disabilitas</t>
-  </si>
-  <si>
-    <t>Non disabilitas</t>
-  </si>
-  <si>
-    <t>tidak</t>
-  </si>
-  <si>
-    <t>Jawa Timur</t>
-  </si>
-  <si>
-    <t>Kota Malang</t>
-  </si>
-  <si>
-    <t>Kedungkandang</t>
-  </si>
-  <si>
-    <t>Buring</t>
-  </si>
-  <si>
-    <t>3573031702000003</t>
-  </si>
-  <si>
-    <t>AHMAD DWI CANDRA GUNAWAN</t>
-  </si>
-  <si>
-    <t>KH MALIK DALAM 1 RT 1 RW 3 BURING</t>
-  </si>
-  <si>
-    <t>60 kg</t>
-  </si>
-  <si>
-    <t>165 cm</t>
-  </si>
-  <si>
-    <t>80 cm</t>
+    <t>status pernikahan</t>
+  </si>
+  <si>
+    <t>penyandang disabilitas</t>
+  </si>
+  <si>
+    <t>pekerjaan</t>
+  </si>
+  <si>
+    <t>Nama Sekolah</t>
+  </si>
+  <si>
+    <t>Kelas / Jenjang</t>
+  </si>
+  <si>
+    <t>Hemoglobin</t>
+  </si>
+  <si>
+    <t>Gigi</t>
+  </si>
+  <si>
+    <t>telinga dan mata</t>
+  </si>
+  <si>
+    <t>kebugaran</t>
+  </si>
+  <si>
+    <t>kadar co</t>
+  </si>
+  <si>
+    <t>Riwayat Imunisasi Rutin Anak Sekolah</t>
+  </si>
+  <si>
+    <t>Diisi jumlah hari aktif  secara  fisik</t>
+  </si>
+  <si>
+    <t>Diisi jumlah hari aktif aktivitas fisik</t>
+  </si>
+  <si>
+    <t>3573036008150003</t>
+  </si>
+  <si>
+    <t>INI ADLAH BARIS CONTOH</t>
+  </si>
+  <si>
+    <t>Belum Menikah</t>
+  </si>
+  <si>
+    <t>Pelajar</t>
+  </si>
+  <si>
+    <t>SDN KOTALAMA 1</t>
+  </si>
+  <si>
+    <t>Jl. Laksamana Martadinata VI B/20</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>tidak ada</t>
+  </si>
+  <si>
+    <t>baik</t>
+  </si>
+  <si>
+    <t>iya lengkap</t>
+  </si>
+  <si>
+    <t>3573031106150005</t>
+  </si>
+  <si>
+    <t>HAPUS AJA JIKA SUDAH MENGISI</t>
+  </si>
+  <si>
+    <t>Jl. Laks Martadinata III</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;Kelas &quot;0"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -571,15 +585,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -587,20 +607,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -941,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.125" style="1" bestFit="1" customWidth="1"/>
@@ -993,76 +1033,76 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>38</v>
+      <c r="AB1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>11</v>
@@ -1078,91 +1118,167 @@
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="5" t="str">
+        <f ca="1">TEXT(DATE(  IF(VALUE(MID(A2,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A2,11,2)), 1900+VALUE(MID(A2,11,2))),  VALUE(MID(A2,9,2)),  IF(VALUE(MID(A2,7,2))&gt;40, VALUE(MID(A2,7,2))-40, VALUE(MID(A2,7,2)))), "mm-dd-yyyy")</f>
+        <v>08-20-2015</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <f>IF(A2&lt;&gt;"",IF(VALUE(MID(A2,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
+        <v>Perempuan</v>
+      </c>
+      <c r="E2" s="4">
+        <v>85230186668</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="7">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="O2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2" ca="1" si="0">TEXT(DATE(IF(VALUE(MID(A2,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A2,11,2)), 1900+VALUE(MID(A2,11,2))), VALUE(MID(A2,9,2)), IF(VALUE(MID(A2,7,2))&gt;40, VALUE(MID(A2,7,2))-40, VALUE(MID(A2,7,2)))), "dd-mm-yyyy")</f>
-        <v>17-02-2000</v>
-      </c>
-      <c r="D2" s="2" t="str">
-        <f t="shared" ref="D2" si="1">IF(A2&lt;&gt;"",IF(VALUE(MID(A2,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
+      <c r="P2" s="4">
+        <v>90</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>13</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W2" s="4">
+        <v>4</v>
+      </c>
+      <c r="X2" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <f t="shared" ref="C3" ca="1" si="0">TEXT(DATE(  IF(VALUE(MID(A3,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A3,11,2)), 1900+VALUE(MID(A3,11,2))),  VALUE(MID(A3,9,2)),  IF(VALUE(MID(A3,7,2))&gt;40, VALUE(MID(A3,7,2))-40, VALUE(MID(A3,7,2)))), "mm-dd-yyyy")</f>
+        <v>06-11-2015</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <f t="shared" ref="D3" si="1">IF(A3&lt;&gt;"",IF(VALUE(MID(A3,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
         <v>Laki-laki</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E3" s="4">
         <v>85230186668</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="I3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="8">
+        <v>5</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="S3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="U3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>34</v>
+      <c r="W3" s="4">
+        <v>4</v>
+      </c>
+      <c r="X3" s="4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Templates/Template_CKGSekolah.xlsx
+++ b/Templates/Template_CKGSekolah.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lihan\AUTOMATION\AutoCKG\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E647BFA-300B-43AF-908A-0249167256B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565F899E-D269-400D-B32C-512C10FC96CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,9 +471,6 @@
     <t>Diisi jumlah hari aktif aktivitas fisik</t>
   </si>
   <si>
-    <t>3573036008150003</t>
-  </si>
-  <si>
     <t>INI ADLAH BARIS CONTOH</t>
   </si>
   <si>
@@ -510,9 +507,6 @@
     <t>iya lengkap</t>
   </si>
   <si>
-    <t>3573031106150005</t>
-  </si>
-  <si>
     <t>HAPUS AJA JIKA SUDAH MENGISI</t>
   </si>
   <si>
@@ -529,15 +523,18 @@
   </si>
   <si>
     <t>60</t>
+  </si>
+  <si>
+    <t>65656565655</t>
+  </si>
+  <si>
+    <t>56565656565656</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;Kelas &quot;0"/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -627,20 +624,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1118,78 +1113,78 @@
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="5" t="str">
+      <c r="C2" s="4" t="str">
         <f ca="1">TEXT(DATE(  IF(VALUE(MID(A2,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A2,11,2)), 1900+VALUE(MID(A2,11,2))),  VALUE(MID(A2,9,2)),  IF(VALUE(MID(A2,7,2))&gt;40, VALUE(MID(A2,7,2))-40, VALUE(MID(A2,7,2)))), "mm-dd-yyyy")</f>
-        <v>08-20-2015</v>
+        <v>05-25-2010</v>
       </c>
       <c r="D2" s="6" t="str">
         <f>IF(A2&lt;&gt;"",IF(VALUE(MID(A2,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
         <v>Perempuan</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>85230186668</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="3">
+        <v>5</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="7">
-        <v>5</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="4">
-        <v>90</v>
-      </c>
-      <c r="Q2" s="4">
+      <c r="S2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="T2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="U2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W2" s="4">
+      <c r="W2" s="3">
         <v>4</v>
       </c>
-      <c r="X2" s="4">
+      <c r="X2" s="3">
         <v>4</v>
       </c>
       <c r="Z2" s="1" t="s">
@@ -1206,78 +1201,78 @@
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="5" t="str">
+      <c r="A3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="str">
         <f t="shared" ref="C3" ca="1" si="0">TEXT(DATE(  IF(VALUE(MID(A3,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A3,11,2)), 1900+VALUE(MID(A3,11,2))),  VALUE(MID(A3,9,2)),  IF(VALUE(MID(A3,7,2))&gt;40, VALUE(MID(A3,7,2))-40, VALUE(MID(A3,7,2)))), "mm-dd-yyyy")</f>
-        <v>06-11-2015</v>
+        <v>08-16-1960</v>
       </c>
       <c r="D3" s="6" t="str">
         <f t="shared" ref="D3" si="1">IF(A3&lt;&gt;"",IF(VALUE(MID(A3,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
-        <v>Laki-laki</v>
-      </c>
-      <c r="E3" s="4">
+        <v>Perempuan</v>
+      </c>
+      <c r="E3" s="3">
         <v>85230186668</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="8">
+      <c r="J3" s="3">
         <v>5</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="N3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="T3" s="4" t="s">
+      <c r="U3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W3" s="4">
+      <c r="W3" s="3">
         <v>4</v>
       </c>
-      <c r="X3" s="4">
+      <c r="X3" s="3">
         <v>4</v>
       </c>
     </row>

--- a/Templates/Template_CKGSekolah.xlsx
+++ b/Templates/Template_CKGSekolah.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lihan\AUTOMATION\AutoCKG\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565F899E-D269-400D-B32C-512C10FC96CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E719AD-1D93-4CBE-BA47-BFF1A49D9161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>ini sudah berisi rumus pencarian tgl lahir dari NIK, kalo tidak yakin dengan ini, pastikan formatnya mm-dd-yyyy</t>
+          <t>ini sudah berisi rumus pencarian tgl lahir dari NIK, kalo tidak yakin dengan ini, isi aja sendiri dan 
+pastikan formatnya mm-dd-yyyy</t>
         </r>
       </text>
     </comment>
@@ -596,7 +597,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -604,34 +605,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1113,17 +1098,17 @@
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="4" t="str">
-        <f ca="1">TEXT(DATE(  IF(VALUE(MID(A2,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A2,11,2)), 1900+VALUE(MID(A2,11,2))),  VALUE(MID(A2,9,2)),  IF(VALUE(MID(A2,7,2))&gt;40, VALUE(MID(A2,7,2))-40, VALUE(MID(A2,7,2)))), "mm-dd-yyyy")</f>
-        <v>05-25-2010</v>
-      </c>
-      <c r="D2" s="6" t="str">
+      <c r="C2" s="3" t="str">
+        <f t="shared" ref="C2:C3" ca="1" si="0">TEXT(DATE(IF(VALUE(MID(A2,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A2,11,2)), 1900+VALUE(MID(A2,11,2))), VALUE(MID(A2,9,2)), IF(VALUE(MID(A2,7,2))&gt;40, VALUE(MID(A2,7,2))-40, VALUE(MID(A2,7,2)))), "dd-mm-yyyy")</f>
+        <v>25-05-2010</v>
+      </c>
+      <c r="D2" s="5" t="str">
         <f>IF(A2&lt;&gt;"",IF(VALUE(MID(A2,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
         <v>Perempuan</v>
       </c>
@@ -1201,17 +1186,17 @@
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="4" t="str">
-        <f t="shared" ref="C3" ca="1" si="0">TEXT(DATE(  IF(VALUE(MID(A3,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A3,11,2)), 1900+VALUE(MID(A3,11,2))),  VALUE(MID(A3,9,2)),  IF(VALUE(MID(A3,7,2))&gt;40, VALUE(MID(A3,7,2))-40, VALUE(MID(A3,7,2)))), "mm-dd-yyyy")</f>
-        <v>08-16-1960</v>
-      </c>
-      <c r="D3" s="6" t="str">
+      <c r="C3" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>16-08-1960</v>
+      </c>
+      <c r="D3" s="5" t="str">
         <f t="shared" ref="D3" si="1">IF(A3&lt;&gt;"",IF(VALUE(MID(A3,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
         <v>Perempuan</v>
       </c>
